--- a/test-data/suppliers.xlsx
+++ b/test-data/suppliers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,6 +409,18 @@
       <c r="C1" t="str">
         <v>Categoría</v>
       </c>
+      <c r="D1" t="str">
+        <v>Dirección</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Localidad</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Provincia</v>
+      </c>
+      <c r="G1" t="str">
+        <v>País</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -420,6 +432,18 @@
       <c r="C2" t="str">
         <v>proveedor</v>
       </c>
+      <c r="D2" t="str">
+        <v>Pueyrredón 440</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Mendoza</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Mendoza</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Argentina</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -431,6 +455,18 @@
       <c r="C3" t="str">
         <v>proveedor</v>
       </c>
+      <c r="D3" t="str">
+        <v>Puerto Madero 10</v>
+      </c>
+      <c r="E3" t="str">
+        <v>CABA</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Capital Federal</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Argentina</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -442,10 +478,22 @@
       <c r="C4" t="str">
         <v>ambos</v>
       </c>
+      <c r="D4" t="str">
+        <v>Av. del Libertador 500</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Vicente López</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Buenos Aires</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Argentina</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>